--- a/All_Code/Q2_yy/Results/Tables/specified_dates_results.xlsx
+++ b/All_Code/Q2_yy/Results/Tables/specified_dates_results.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表1购电" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表2储能" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表3紧急购电" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="表1购电" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="表2储能" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="表3紧急购电" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -506,22 +506,22 @@
         <v>523.9341079845428</v>
       </c>
       <c r="F2" t="n">
-        <v>262.373968898108</v>
+        <v>712.7475984201584</v>
       </c>
       <c r="G2" t="n">
-        <v>42.18601403495904</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>71129.23586615705</v>
+        <v>71479.41512057408</v>
       </c>
       <c r="I2" t="n">
-        <v>43219.15781559237</v>
+        <v>43233.43886054323</v>
       </c>
       <c r="J2" t="n">
-        <v>1878.815964223687</v>
+        <v>2334.685304105849</v>
       </c>
       <c r="K2" t="n">
-        <v>45097.97377981606</v>
+        <v>45568.12416464908</v>
       </c>
     </row>
     <row r="3">
@@ -540,25 +540,25 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>279.1660666714201</v>
+        <v>279.1660666714203</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>131.276454447118</v>
       </c>
       <c r="G3" t="n">
-        <v>109.2171957648516</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>40084.63723559067</v>
+        <v>42324.35444032646</v>
       </c>
       <c r="I3" t="n">
-        <v>23483.1621752637</v>
+        <v>24565.92664404374</v>
       </c>
       <c r="J3" t="n">
-        <v>765.365808552584</v>
+        <v>650.328441349877</v>
       </c>
       <c r="K3" t="n">
-        <v>24248.52798381629</v>
+        <v>25216.25508539362</v>
       </c>
     </row>
     <row r="4">
@@ -577,25 +577,25 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>591.2923628133744</v>
+        <v>591.292362813374</v>
       </c>
       <c r="F4" t="n">
         <v>840.9012963252718</v>
       </c>
       <c r="G4" t="n">
-        <v>120.5967002439849</v>
+        <v>21.60716812100043</v>
       </c>
       <c r="H4" t="n">
-        <v>75524.72345608671</v>
+        <v>76040.75187439992</v>
       </c>
       <c r="I4" t="n">
-        <v>48009.8645473041</v>
+        <v>48103.79541004973</v>
       </c>
       <c r="J4" t="n">
-        <v>317.9708791814707</v>
+        <v>470.1375206705101</v>
       </c>
       <c r="K4" t="n">
-        <v>48327.83542648557</v>
+        <v>48573.93293072024</v>
       </c>
     </row>
     <row r="5">
@@ -608,31 +608,31 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>968.1981706289636</v>
+        <v>968.1981706289632</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>853.5975807774944</v>
+        <v>853.5975807774945</v>
       </c>
       <c r="F5" t="n">
-        <v>249.8110043938749</v>
+        <v>719.97074733483</v>
       </c>
       <c r="G5" t="n">
-        <v>289.776625</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>97224.81262222344</v>
+        <v>100109.3603763508</v>
       </c>
       <c r="I5" t="n">
-        <v>63956.91245250536</v>
+        <v>64432.16192068168</v>
       </c>
       <c r="J5" t="n">
-        <v>1718.927169333249</v>
+        <v>2296.987107319518</v>
       </c>
       <c r="K5" t="n">
-        <v>65675.8396218386</v>
+        <v>66729.14902800121</v>
       </c>
     </row>
   </sheetData>
@@ -693,16 +693,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8554.22439029944</v>
+        <v>4499.999999999894</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1514.718154555469</v>
+        <v>6000.000000000095</v>
       </c>
       <c r="F2" t="n">
-        <v>1393.350241688316</v>
+        <v>6000.000000000096</v>
       </c>
     </row>
     <row r="3">
@@ -717,16 +717,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1666.666666666667</v>
+        <v>833.3333333333334</v>
       </c>
       <c r="D3" t="n">
-        <v>4882.10134213696</v>
+        <v>5185.109766848524</v>
       </c>
       <c r="E3" t="n">
-        <v>1514.718154555469</v>
+        <v>6000.000000000095</v>
       </c>
       <c r="F3" t="n">
-        <v>1393.350241688316</v>
+        <v>6000.000000000096</v>
       </c>
     </row>
     <row r="4">
@@ -741,16 +741,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6005.928028766265</v>
+        <v>6107.014474656956</v>
       </c>
       <c r="D4" t="n">
-        <v>2772.554614885431</v>
+        <v>3454.890233151476</v>
       </c>
       <c r="E4" t="n">
-        <v>1514.718154555469</v>
+        <v>6000.000000000095</v>
       </c>
       <c r="F4" t="n">
-        <v>1393.350241688316</v>
+        <v>6000.000000000096</v>
       </c>
     </row>
     <row r="5">
@@ -765,16 +765,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3854.825854089607</v>
+        <v>5440.976849094623</v>
       </c>
       <c r="D5" t="n">
-        <v>254.722783333333</v>
+        <v>713.8729722387812</v>
       </c>
       <c r="E5" t="n">
-        <v>1514.718154555469</v>
+        <v>6000.000000000095</v>
       </c>
       <c r="F5" t="n">
-        <v>1393.350241688316</v>
+        <v>6000.000000000096</v>
       </c>
     </row>
     <row r="6">
@@ -792,13 +792,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>5798.993332493549</v>
+        <v>5699.562497808012</v>
       </c>
       <c r="E6" t="n">
-        <v>1514.718154555469</v>
+        <v>6000.000000000095</v>
       </c>
       <c r="F6" t="n">
-        <v>1393.350241688316</v>
+        <v>6000.000000000096</v>
       </c>
     </row>
     <row r="7">
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>5333.333333333439</v>
       </c>
       <c r="D7" t="n">
-        <v>2666.991449986966</v>
+        <v>2940.437502191987</v>
       </c>
       <c r="E7" t="n">
-        <v>1514.718154555469</v>
+        <v>6000.000000000095</v>
       </c>
       <c r="F7" t="n">
-        <v>1393.350241688316</v>
+        <v>6000.000000000096</v>
       </c>
     </row>
     <row r="8">
@@ -837,16 +837,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2867.939719997421</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2278.907512473861</v>
+        <v>6000.000000000183</v>
       </c>
       <c r="F8" t="n">
-        <v>2358.752498208346</v>
+        <v>6000.000000000184</v>
       </c>
     </row>
     <row r="9">
@@ -861,16 +861,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>976.6233404955235</v>
+        <v>794.7432332985373</v>
       </c>
       <c r="D9" t="n">
-        <v>1646.105376167546</v>
+        <v>1973.36794495243</v>
       </c>
       <c r="E9" t="n">
-        <v>2278.907512473861</v>
+        <v>6000.000000000183</v>
       </c>
       <c r="F9" t="n">
-        <v>2358.752498208346</v>
+        <v>6000.000000000184</v>
       </c>
     </row>
     <row r="10">
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4105.114415863653</v>
+        <v>3864.306117325726</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2278.907512473861</v>
+        <v>6000.000000000183</v>
       </c>
       <c r="F10" t="n">
-        <v>2358.752498208346</v>
+        <v>6000.000000000184</v>
       </c>
     </row>
     <row r="11">
@@ -909,16 +909,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3550.431924805216</v>
+        <v>3110.540704872364</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>2278.907512473861</v>
+        <v>6000.000000000183</v>
       </c>
       <c r="F11" t="n">
-        <v>2358.752498208346</v>
+        <v>6000.000000000184</v>
       </c>
     </row>
     <row r="12">
@@ -936,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>5577.642883946357</v>
+        <v>5814.555476219962</v>
       </c>
       <c r="E12" t="n">
-        <v>2278.907512473861</v>
+        <v>6000.000000000183</v>
       </c>
       <c r="F12" t="n">
-        <v>2358.752498208346</v>
+        <v>6000.000000000184</v>
       </c>
     </row>
     <row r="13">
@@ -957,16 +957,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>5333.333333333537</v>
       </c>
       <c r="D13" t="n">
-        <v>2019.479867666133</v>
+        <v>2825.444523780038</v>
       </c>
       <c r="E13" t="n">
-        <v>2278.907512473861</v>
+        <v>6000.000000000183</v>
       </c>
       <c r="F13" t="n">
-        <v>2358.752498208346</v>
+        <v>6000.000000000184</v>
       </c>
     </row>
     <row r="14">
@@ -981,16 +981,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8487.575188624953</v>
+        <v>4499.999999999704</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1661.182330237542</v>
+        <v>6000.000000000266</v>
       </c>
       <c r="F14" t="n">
-        <v>1879.876104127257</v>
+        <v>6000.000000000266</v>
       </c>
     </row>
     <row r="15">
@@ -1005,16 +1005,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1666.666666666667</v>
+        <v>833.3333333333334</v>
       </c>
       <c r="D15" t="n">
-        <v>4995.725998716445</v>
+        <v>5330.27818997839</v>
       </c>
       <c r="E15" t="n">
-        <v>1661.182330237542</v>
+        <v>6000.000000000266</v>
       </c>
       <c r="F15" t="n">
-        <v>1879.876104127257</v>
+        <v>6000.000000000266</v>
       </c>
     </row>
     <row r="16">
@@ -1029,16 +1029,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6063.044071183051</v>
+        <v>6075.861103408506</v>
       </c>
       <c r="D16" t="n">
-        <v>1896.615716666666</v>
+        <v>3309.721810021611</v>
       </c>
       <c r="E16" t="n">
-        <v>1661.182330237542</v>
+        <v>6000.000000000266</v>
       </c>
       <c r="F16" t="n">
-        <v>1879.876104127257</v>
+        <v>6000.000000000266</v>
       </c>
     </row>
     <row r="17">
@@ -1053,16 +1053,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2881.585328330685</v>
+        <v>5430.75007315569</v>
       </c>
       <c r="D17" t="n">
-        <v>352.8080982230132</v>
+        <v>680.3550530169989</v>
       </c>
       <c r="E17" t="n">
-        <v>1661.182330237542</v>
+        <v>6000.000000000266</v>
       </c>
       <c r="F17" t="n">
-        <v>1879.876104127257</v>
+        <v>6000.000000000266</v>
       </c>
     </row>
     <row r="18">
@@ -1080,13 +1080,13 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5286.308478369519</v>
+        <v>5833.333333333334</v>
       </c>
       <c r="E18" t="n">
-        <v>1661.182330237542</v>
+        <v>6000.000000000266</v>
       </c>
       <c r="F18" t="n">
-        <v>1879.876104127257</v>
+        <v>6000.000000000266</v>
       </c>
     </row>
     <row r="19">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>5333.333333333629</v>
       </c>
       <c r="D19" t="n">
-        <v>2741.803027915947</v>
+        <v>2806.666666666667</v>
       </c>
       <c r="E19" t="n">
-        <v>1661.182330237542</v>
+        <v>6000.000000000266</v>
       </c>
       <c r="F19" t="n">
-        <v>1879.876104127257</v>
+        <v>6000.000000000266</v>
       </c>
     </row>
     <row r="20">
@@ -1125,16 +1125,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6666.666666666667</v>
+        <v>4499.999999999608</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>3804.486177664382</v>
+        <v>6000.000000000354</v>
       </c>
       <c r="F20" t="n">
-        <v>1398.640425118601</v>
+        <v>6000.000000000359</v>
       </c>
     </row>
     <row r="21">
@@ -1149,16 +1149,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1809.872571240632</v>
+        <v>1666.666666666667</v>
       </c>
       <c r="D21" t="n">
-        <v>1073.663063546152</v>
+        <v>1508.333333333333</v>
       </c>
       <c r="E21" t="n">
-        <v>3804.486177664382</v>
+        <v>6000.000000000354</v>
       </c>
       <c r="F21" t="n">
-        <v>1398.640425118601</v>
+        <v>6000.000000000359</v>
       </c>
     </row>
     <row r="22">
@@ -1173,16 +1173,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5611.729862272197</v>
+        <v>5833.333333333334</v>
       </c>
       <c r="D22" t="n">
-        <v>6444.558799116232</v>
+        <v>7806.666666666668</v>
       </c>
       <c r="E22" t="n">
-        <v>3804.486177664382</v>
+        <v>6000.000000000354</v>
       </c>
       <c r="F22" t="n">
-        <v>1398.640425118601</v>
+        <v>6000.000000000359</v>
       </c>
     </row>
     <row r="23">
@@ -1197,16 +1197,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5707.155244797178</v>
+        <v>8242.95890428947</v>
       </c>
       <c r="D23" t="n">
-        <v>2220.109416666667</v>
+        <v>2761.796712474469</v>
       </c>
       <c r="E23" t="n">
-        <v>3804.486177664382</v>
+        <v>6000.000000000354</v>
       </c>
       <c r="F23" t="n">
-        <v>1398.640425118601</v>
+        <v>6000.000000000359</v>
       </c>
     </row>
     <row r="24">
@@ -1224,13 +1224,13 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>6104.281831216453</v>
+        <v>5683.745833498252</v>
       </c>
       <c r="E24" t="n">
-        <v>3804.486177664382</v>
+        <v>6000.000000000354</v>
       </c>
       <c r="F24" t="n">
-        <v>1398.640425118601</v>
+        <v>6000.000000000359</v>
       </c>
     </row>
     <row r="25">
@@ -1245,16 +1245,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>5333.333333333727</v>
       </c>
       <c r="D25" t="n">
-        <v>2356.941786176806</v>
+        <v>2956.254166501746</v>
       </c>
       <c r="E25" t="n">
-        <v>3804.486177664382</v>
+        <v>6000.000000000354</v>
       </c>
       <c r="F25" t="n">
-        <v>1398.640425118601</v>
+        <v>6000.000000000359</v>
       </c>
     </row>
   </sheetData>
@@ -1268,7 +1268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1296,11 +1296,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3:10-3:30</t>
+          <t>0:20-0:30</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36.11194838479616</v>
+        <v>25.5129780916709</v>
       </c>
     </row>
     <row r="3">
@@ -1311,11 +1311,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3:40-4:00</t>
+          <t>1:00-1:30</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.46517833063183</v>
+        <v>70.57579321392291</v>
       </c>
     </row>
     <row r="4">
@@ -1326,11 +1326,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4:50-5:20</t>
+          <t>3:10-3:30</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.22066686008645</v>
+        <v>36.11194838479605</v>
       </c>
     </row>
     <row r="5">
@@ -1341,11 +1341,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6:40-7:00</t>
+          <t>3:40-4:00</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14.94031123877375</v>
+        <v>20.46517833063183</v>
       </c>
     </row>
     <row r="6">
@@ -1356,11 +1356,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9:00-9:10</t>
+          <t>4:50-5:20</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4.822601781235448</v>
+        <v>29.22066686008657</v>
       </c>
     </row>
     <row r="7">
@@ -1371,11 +1371,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:20-16:20</t>
+          <t>6:40-7:00</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>174.7052594082688</v>
+        <v>14.94031123877383</v>
       </c>
     </row>
     <row r="8">
@@ -1386,11 +1386,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:30-17:20</t>
+          <t>9:00-9:10</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>75.63281995618104</v>
+        <v>4.822601781235448</v>
       </c>
     </row>
     <row r="9">
@@ -1401,11 +1401,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18:10-18:20</t>
+          <t>10:50-11:30</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.78785312498178</v>
+        <v>101.0864458906915</v>
       </c>
     </row>
     <row r="10">
@@ -1416,11 +1416,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18:40-19:10</t>
+          <t>15:20-16:20</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>29.31745130799607</v>
+        <v>174.7052594082684</v>
       </c>
     </row>
     <row r="11">
@@ -1431,11 +1431,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20:00-20:20</t>
+          <t>16:30-17:20</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>46.28251457245352</v>
+        <v>75.63281995618115</v>
       </c>
     </row>
     <row r="12">
@@ -1446,56 +1446,56 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23:30-23:40</t>
+          <t>18:10-18:20</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.21186345302124</v>
+        <v>2.787853124981893</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1:20-1:30</t>
+          <t>18:40-19:10</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5.806425182182238</v>
+        <v>29.31745130799604</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3:00-3:30</t>
+          <t>20:00-20:20</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38.25627274636372</v>
+        <v>46.28251457245358</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3:50-4:10</t>
+          <t>23:30-23:40</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>29.29567625565272</v>
+        <v>14.21186345302135</v>
       </c>
     </row>
     <row r="16">
@@ -1506,11 +1506,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5:00-5:10</t>
+          <t>1:20-1:30</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9.868949665947184</v>
+        <v>5.806425182182352</v>
       </c>
     </row>
     <row r="17">
@@ -1521,11 +1521,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5:20-5:30</t>
+          <t>3:00-3:30</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7.650840608100339</v>
+        <v>38.25627274636378</v>
       </c>
     </row>
     <row r="18">
@@ -1536,11 +1536,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5:50-6:20</t>
+          <t>3:50-4:10</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>73.848590499121</v>
+        <v>29.29567625565278</v>
       </c>
     </row>
     <row r="19">
@@ -1551,11 +1551,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18:40-18:50</t>
+          <t>5:00-5:10</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9.758819197708029</v>
+        <v>9.868949665947071</v>
       </c>
     </row>
     <row r="20">
@@ -1566,146 +1566,146 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19:00-19:10</t>
+          <t>5:20-5:40</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.95465412472721</v>
+        <v>24.22857480881464</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2:10-2:20</t>
+          <t>5:50-6:20</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.784673765884577</v>
+        <v>43.45110338700698</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5:00-5:10</t>
+          <t>8:30-8:40</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4.610689408810003</v>
+        <v>10.35185522848258</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:30-14:50</t>
+          <t>9:00-9:10</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>50.81681844365335</v>
+        <v>21.10521139792286</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>22:20-22:30</t>
+          <t>18:40-18:50</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26.11656948074631</v>
+        <v>9.758819197707997</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1:10-1:20</t>
+          <t>2:10-2:20</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4.034806877941719</v>
+        <v>5.784673765884691</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3:30-3:50</t>
+          <t>5:00-5:10</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>41.99476147059636</v>
+        <v>4.610689408810003</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10:30-10:50</t>
+          <t>10:40-10:50</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>121.424642122006</v>
+        <v>12.81703222545593</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12:50-13:00</t>
+          <t>14:30-15:10</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>39.24557295259694</v>
+        <v>80.99582128735324</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:20-16:30</t>
+          <t>22:20-22:30</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.2998526151120586</v>
+        <v>26.11656948074619</v>
       </c>
     </row>
     <row r="30">
@@ -1716,11 +1716,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:50-17:00</t>
+          <t>1:10-1:20</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.8080006783159206</v>
+        <v>4.034806877941605</v>
       </c>
     </row>
     <row r="31">
@@ -1731,11 +1731,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:20-17:30</t>
+          <t>3:30-3:50</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>14.51214917928019</v>
+        <v>46.27221095587629</v>
       </c>
     </row>
     <row r="32">
@@ -1746,11 +1746,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18:10-19:10</t>
+          <t>10:30-11:30</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>73.21715949266547</v>
+        <v>343.0281131831422</v>
       </c>
     </row>
     <row r="33">
@@ -1761,11 +1761,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19:20-19:30</t>
+          <t>12:40-13:00</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2.285312032119236</v>
+        <v>49.29221692993326</v>
       </c>
     </row>
     <row r="34">
@@ -1776,11 +1776,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:40-20:00</t>
+          <t>16:20-16:30</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>52.077127725899</v>
+        <v>0.2998526151120586</v>
       </c>
     </row>
     <row r="35">
@@ -1791,11 +1791,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20:30-20:40</t>
+          <t>16:50-17:00</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.221562142028915</v>
+        <v>0.8080006783159206</v>
       </c>
     </row>
     <row r="36">
@@ -1806,11 +1806,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21:50-22:00</t>
+          <t>17:20-17:30</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7.52694296531547</v>
+        <v>14.51214917928041</v>
       </c>
     </row>
     <row r="37">
@@ -1821,11 +1821,86 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>18:10-19:10</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>73.21715949266542</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>19:20-19:30</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2.285312032119236</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>19:40-20:00</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>52.07712772589889</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>20:30-20:40</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.8804819884061317</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>21:50-22:00</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>7.526942965315584</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>23:30-23:40</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>5.440771495455351</v>
+      <c r="C42" t="n">
+        <v>5.440771495455465</v>
       </c>
     </row>
   </sheetData>
